--- a/artfynd/A 56983-2021 artfynd.xlsx
+++ b/artfynd/A 56983-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>64721294</v>
+        <v>135208706</v>
       </c>
       <c r="B5" t="n">
-        <v>101325</v>
+        <v>106236</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,40 +1032,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Enerums gamla bygata, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620445</v>
+        <v>620498</v>
       </c>
       <c r="R5" t="n">
-        <v>6352579</v>
+        <v>6352546</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,12 +1086,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-04-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-04-01</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Enstaka i innerslänten</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,15 +1111,119 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Edvin Åhman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Edvin Åhman, Christine Sandberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>64721294</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Enerums gamla bygata, Öl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>620445</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6352579</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-04-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-04-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Ulla-Britt Andersson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Ulla-Britt Andersson, Thomas Gunnarsson, Tommy Knutsson, Mikael Jeppson, Annika Sohlman</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>

--- a/artfynd/A 56983-2021 artfynd.xlsx
+++ b/artfynd/A 56983-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -805,6 +810,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82738567</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64721396</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1018,6 +1033,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64721316</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135208706</t>
         </is>
       </c>
     </row>
@@ -1228,8 +1253,20 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64721294</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 56983-2021 artfynd.xlsx
+++ b/artfynd/A 56983-2021 artfynd.xlsx
@@ -1044,7 +1044,7 @@
         <v>135208706</v>
       </c>
       <c r="B5" t="n">
-        <v>106236</v>
+        <v>106291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56983-2021 artfynd.xlsx
+++ b/artfynd/A 56983-2021 artfynd.xlsx
@@ -1044,7 +1044,7 @@
         <v>135208706</v>
       </c>
       <c r="B5" t="n">
-        <v>106291</v>
+        <v>106318</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 56983-2021 artfynd.xlsx
+++ b/artfynd/A 56983-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1041,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>64721294</v>
+        <v>135208706</v>
       </c>
       <c r="B5" t="n">
-        <v>101325</v>
+        <v>106323</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,40 +1052,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Enerums gamla bygata, Öl</t>
+          <t>Vägområde, Öl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620445</v>
+        <v>620498</v>
       </c>
       <c r="R5" t="n">
-        <v>6352579</v>
+        <v>6352546</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,12 +1106,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-04-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-04-01</t>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Enstaka i innerslänten</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,20 +1131,129 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Edvin Åhman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Edvin Åhman, Christine Sandberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135208706</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>64721294</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Enerums gamla bygata, Öl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>620445</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6352579</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-04-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-04-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Ulla-Britt Andersson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Ulla-Britt Andersson, Thomas Gunnarsson, Tommy Knutsson, Mikael Jeppson, Annika Sohlman</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/64721294</t>
         </is>
@@ -1154,6 +1265,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56983-2021 artfynd.xlsx
+++ b/artfynd/A 56983-2021 artfynd.xlsx
@@ -1044,7 +1044,7 @@
         <v>135208706</v>
       </c>
       <c r="B5" t="n">
-        <v>106323</v>
+        <v>106325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
